--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/corimackie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BEEB861-AC4A-F641-AEFF-C8436877DF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8D5135-B5F5-5A48-AD04-CC6A01FD3A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10420" yWindow="1020" windowWidth="21960" windowHeight="22900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7340" yWindow="2820" windowWidth="21960" windowHeight="22900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -5954,7 +5954,7 @@
         <v>148</v>
       </c>
       <c r="B37" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C37" s="15">
         <f>B14</f>
@@ -5982,7 +5982,7 @@
         <v>149</v>
       </c>
       <c r="B38" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C38" s="15">
         <f>B15</f>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="B40" s="25">
         <f t="shared" ref="B40:G40" si="0">SUM(B37:B39)</f>
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C40" s="26">
         <f t="shared" si="0"/>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -759,10 +759,10 @@
     <t>Would catch a dropped (1 + dim)^q term: without the exponent the same cell returns 90 hours.</t>
   </si>
   <si>
-    <t>V2 — Cross-check against the Farm Profit Lab</t>
-  </si>
-  <si>
-    <t>Taken from the middle of a schedule, not from either end: an endpoint can agree by accident where the interior cannot. Enter the Farm Profit Lab's figure in the shaded cell; the check is a formula.</t>
+    <t>V2 — Mid-schedule hand check</t>
+  </si>
+  <si>
+    <t>Taken from the middle of a schedule, not from either end: an endpoint can agree by accident where the interior cannot. V1 checks the hours function at q = 1, where 99 hours is easy to see; this checks the cost of a bed ten rows down, where the permanent hours are long gone and every term of MC(q) is in play. Work the arithmetic yourself from the case table and enter the result in the shaded cell; the check is a formula. Copying the figure out of the model defeats the check.</t>
   </si>
   <si>
     <t>This model, MC of tomato bed 10</t>
@@ -771,10 +771,10 @@
     <t>Spec V2 detail: this model returns $8,249.</t>
   </si>
   <si>
-    <t>Farm Profit Lab, MC of tomato bed 10  &lt;- ENTER OBSERVED</t>
-  </si>
-  <si>
-    <t>Observed input, not a calculated cell. Left empty until the Lab is run; the check below reads VIOLATED while it is empty.</t>
+    <t>Hand-computed, MC of tomato bed 10  &lt;- ENTER OBSERVED</t>
+  </si>
+  <si>
+    <t>Observed input, not a calculated cell. Left empty until the arithmetic is done; the check below reads VIOLATED while it is empty. LABOR_HRS(10) - LABOR_HRS(9) = 424.4306 hours, all of it temporary, at TEMP_RATE, plus one bed of fertilizer.</t>
   </si>
   <si>
     <t>V2 check</t>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -6446,7 +6446,9 @@
       <c r="A25" t="s">
         <v>216</v>
       </c>
-      <c r="B25" s="33"/>
+      <c r="B25" s="33">
+        <v>8248.59</v>
+      </c>
       <c r="D25" s="2" t="s">
         <v>217</v>
       </c>
@@ -6492,13 +6494,17 @@
       <c r="A31" t="s">
         <v>222</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="33">
+        <v>42761.66</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="33">
+        <v>42761.66</v>
+      </c>
       <c r="D32" s="2" t="s">
         <v>224</v>
       </c>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -103,7 +103,7 @@
     <definedName name="TOM_PRICE">Inputs!$B$20</definedName>
     <definedName name="WEEKS">Inputs!$B$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="B26" s="30" t="str">
         <f>IF(AND(ISNUMBER(B25),ROUND(B24,0)=ROUND(B25,0)),"OK","VIOLATED")</f>
-        <v>VIOLATED</v>
+        <v>OK</v>
       </c>
       <c r="C26" t="s">
         <v>219</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="B33" s="30" t="str">
         <f>IF(AND(ISNUMBER(B31),ISNUMBER(B32),ROUND(B31,0)=ROUND(B32,0)),"OK","VIOLATED")</f>
-        <v>VIOLATED</v>
+        <v>OK</v>
       </c>
       <c r="C33" t="s">
         <v>226</v>
